--- a/AAII_Financials/Quarterly/HBRIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HBRIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="92">
   <si>
     <t>HBRIY</t>
   </si>
@@ -656,111 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -803,32 +811,38 @@
       <c r="P8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S8" s="3">
         <v>1183600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1230000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>713400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>871300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>772500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>625000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>497000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>546100</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -871,32 +885,38 @@
       <c r="P9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="3">
         <v>951500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1220400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>159400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>183400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>268400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>231600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>236600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>218800</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -939,32 +959,38 @@
       <c r="P10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S10" s="3">
         <v>232100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>9600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>554000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>687900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>504100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>393400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>260400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>327300</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -989,8 +1015,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1033,32 +1061,38 @@
       <c r="P12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" s="3">
         <v>130800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>4300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>12600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>8700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>27800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>16000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1125,8 +1159,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1169,32 +1209,38 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3">
         <v>723500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>514600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>41500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3">
         <v>244900</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1237,32 +1283,38 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="3">
         <v>315000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>240200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>369900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>346500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>172800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>185600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>242400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>180500</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,8 +1336,10 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1328,32 +1382,38 @@
       <c r="P17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" s="3">
         <v>1690500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1410500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>585900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>543800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>427000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>439500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>604600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>404700</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1396,32 +1456,38 @@
       <c r="P18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" s="3">
         <v>-506900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-180500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>127500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>327500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>345500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>185500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-107600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,8 +1512,10 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1490,32 +1558,38 @@
       <c r="P20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" s="3">
         <v>-187300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>34000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-11700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-66600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-44500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-104000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-152000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-64500</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1558,32 +1632,38 @@
       <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" s="3">
         <v>-195600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>577000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>485700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>607400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>509000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>267100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>227700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>257400</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1626,32 +1706,38 @@
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" s="3">
         <v>59200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>77800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>133200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>141000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>118100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>106200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>103100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>80500</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1694,32 +1780,38 @@
       <c r="P23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" s="3">
         <v>-753400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-224300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-17400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>119900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>182900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-24700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-362700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1762,32 +1854,38 @@
       <c r="P24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S24" s="3">
         <v>-129500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-69800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-60000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>7500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>167900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-114800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-55900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-40200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,8 +1952,14 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1898,32 +2002,38 @@
       <c r="P26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S26" s="3">
         <v>-623900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-154500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>42600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>112400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>15000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>90100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-306800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>36600</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1966,32 +2076,38 @@
       <c r="P27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" s="3">
         <v>-623900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-154500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>42600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>112400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>15000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>90100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-306800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>36600</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2174,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2102,32 +2224,38 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>1100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>8200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>20000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>8300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>12300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2322,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,8 +2396,14 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2306,32 +2446,38 @@
       <c r="P32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" s="3">
         <v>187300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-34000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>11700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>66600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>44500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>104000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>152000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2374,32 +2520,38 @@
       <c r="P33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" s="3">
         <v>-623900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-154500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>43700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>120600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>35000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>98400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-294500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,8 +2618,14 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2510,105 +2668,117 @@
       <c r="P35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S35" s="3">
         <v>-623900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-154500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>43700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>120600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>35000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>98400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-294500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2803,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,103 +2831,111 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="F41" s="3">
         <v>846000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>846000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2711000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2711000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>805000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>805000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>539000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>539000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>286000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>286000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>493500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>493500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>500000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>445400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>139700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>198100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>253500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>244600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>180000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>365400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>307500</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F42" s="3">
         <v>65000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>65000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>24000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>24000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>25000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>25000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2769,17 +2949,17 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>24000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>222600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
@@ -2789,313 +2969,343 @@
       <c r="V42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1966000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1966000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1765000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1765000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2260000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2260000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2061000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2061000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>852000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>852000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>504000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>504000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>904700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>904700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>549000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>461300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>277400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>378900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>393100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>282300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>307000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>340600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>307900</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>646000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>646000</v>
+      </c>
+      <c r="F44" s="3">
         <v>398000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>398000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>388000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>388000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>368000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>368000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>167000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>167000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>217000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>217000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>174200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>174200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>143000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>160500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>13300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>16300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>16100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>12500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>18500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>13500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F45" s="3">
         <v>972000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>972000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>730000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>730000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>572000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>572000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>90000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>90000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>316000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>316000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>81400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>81400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>126000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>14100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>130900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>55300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>39200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>182600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>79100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>111100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4339000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4339000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4113000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4113000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6113000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6113000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3917000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3917000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1648000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1648000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1546000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1546000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1653800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1653800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2127000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1289800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>561300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>648600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>701900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>722000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>584600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>830600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>698900</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F47" s="3">
         <v>22000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>22000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>12000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>12000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>7000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>7000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3108,171 +3318,189 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R47" s="3">
         <v>18000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>342200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>230400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>231100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>227200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>159800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>165100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>160800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16459000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>16459000</v>
+      </c>
+      <c r="F48" s="3">
         <v>13706000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13706000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14864000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14864000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>15234000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>15234000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5329000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5329000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5468000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5468000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6113200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6113200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6425000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7120900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2306900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2481800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2762900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2245600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2177500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2381000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2678600</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10915000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10915000</v>
+      </c>
+      <c r="F49" s="3">
         <v>10811000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>10811000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11010000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11010000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>10776000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>10776000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2544000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2544000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2474000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2474000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2282100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2282100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2207000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1444100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>983600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1174800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1111400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1053400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1322100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1302700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1270500</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3567,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,76 +3641,88 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>279000</v>
+      </c>
+      <c r="F52" s="3">
         <v>303000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>303000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>445000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>445000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>213000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>213000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>366000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>366000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>342000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>342000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>395100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>395100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>339000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>1199100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1556100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1483900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1434100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1619900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1461500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1349600</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,76 +3789,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32185000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>32185000</v>
+      </c>
+      <c r="F54" s="3">
         <v>29093000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29093000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>32591000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>32591000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>30277000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>30277000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9895000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>9895000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9916000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9916000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10824700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10824700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>12566000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9482500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5281300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>6092400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6287300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5614900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5869200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>6136600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>6159000</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3895,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,416 +3923,454 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1114000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1114000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1865000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1865000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1365000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1365000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>855000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>855000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>680000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>680000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>871200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>871200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>47000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>434600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>394200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>301900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>320400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>375600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>310700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>525200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>383400</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1282000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1282000</v>
+      </c>
+      <c r="F58" s="3">
         <v>404000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>404000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1378000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1378000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1255000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1255000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>256000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>256000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>232000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>232000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>234500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>234500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>243000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2262600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2194600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>149700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>161600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>332800</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3278000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3278000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2443000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2443000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2861000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2861000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2994000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2994000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>925000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>925000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1104000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1104000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1879300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1879300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3124000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>635000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>260300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>245200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>95700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>120300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>344000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>298400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>146700</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6207000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6207000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3961000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3961000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6126000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6126000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5614000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5614000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2036000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2036000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2016000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2016000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2985000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2985000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4096000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1039600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2849100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>696800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>577700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>495900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>654700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>823600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>862900</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6393000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6393000</v>
+      </c>
+      <c r="F61" s="3">
         <v>5386000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5386000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5635000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5635000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4766000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4766000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1062000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1062000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1045000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1045000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1012900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1012900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1820000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2241100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>607300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2752600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3097900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2552000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2802300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2972600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2700900</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7504000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>7504000</v>
+      </c>
+      <c r="F62" s="3">
         <v>7040000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7040000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>7465000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>7465000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>7458000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>7458000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3985000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3985000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4005000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4005000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4350900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4350900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5224000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>5157300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1334700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1511500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1501600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1541000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1648200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1723500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1726100</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4437,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4511,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,76 +4585,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25540000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25540000</v>
+      </c>
+      <c r="F66" s="3">
         <v>22887000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>22887000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>26154000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>26154000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>24026000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24026000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8421000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8421000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8363000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8363000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9411000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9411000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>11545000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8415200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4791100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4960900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5177200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4588900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5105200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5519700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>5289900</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4691,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4761,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4835,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4909,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,76 +4983,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>282000</v>
+      </c>
+      <c r="F72" s="3">
         <v>53000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>53000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>399000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>399000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>807000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>807000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1055000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1055000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1093000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1093000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1211500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1211500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1456000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-888300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-197200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>475600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>459800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>380100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>153600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>258500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>487000</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +5131,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5205,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,76 +5279,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4601000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4601000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4181000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4181000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4467000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4467000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4688000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4688000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1474000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1474000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1553000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1553000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1413700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1413700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1067300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>490200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1131500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1110100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1026000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>764000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>616900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>869100</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,81 +5427,93 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5166,32 +5556,38 @@
       <c r="P81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S81" s="3">
         <v>-623900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-154500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>43700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>120600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>35000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>98400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-294500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,76 +5612,84 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>767000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>767000</v>
+      </c>
+      <c r="F83" s="3">
         <v>576500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>576500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>286500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>286500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>355000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>355000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>358000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>358000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>336700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>336700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>375500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>375500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>406700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>498600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>723500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>369900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>346500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>208000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>185600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>487300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>180500</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5756,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5830,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5904,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5978,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,76 +6052,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1386500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1386500</v>
+      </c>
+      <c r="F89" s="3">
         <v>470000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>470000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1223000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1223000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>331000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>331000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>476500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>476500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>331500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>331500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>743500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>743500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>634200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>427300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>946100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>564100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>544600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>498200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>224600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>204000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,76 +6158,84 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-427000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-427000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-444500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-444500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-454500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-454500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-465500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-465500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-156000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-156000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-183500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-183500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-165500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-165500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-153000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-243900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-354200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-138100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-103300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-115500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-164300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-139500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-136100</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6302,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,76 +6376,88 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1638500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1638500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-473000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-473000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-434000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-434000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-974000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-974000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-164500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-164500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-210500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-210500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-136000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-136000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-156600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-136200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-155300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-146300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-115900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-100500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-196400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-113900</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,56 +6482,58 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>89500</v>
+      </c>
+      <c r="F96" s="3">
         <v>123500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>123500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>133000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>133000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>49500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>49500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>50000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>50000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>45500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>45500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>49500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>49500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>46400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6084,8 +6552,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6626,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6700,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,208 +6774,232 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>647000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-909500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-909500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>163000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>163000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>800000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>800000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-185500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-185500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-220000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-220000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-613500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-613500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-649100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-177800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-221100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-481900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-402400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-314100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-212600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-139500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-124600</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-18500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-18500</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-12100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-12100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>1800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-5100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-3600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-19000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-4800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>398500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>398500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-917000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-917000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>951000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>951000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>138500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>138500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>126500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>126500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-104000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-104000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-172400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-31400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-58400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-55400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>8900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>64600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-185400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>57900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>51600</v>
       </c>
     </row>
